--- a/Data/data_by_8_cyl.xlsx
+++ b/Data/data_by_8_cyl.xlsx
@@ -12,6 +12,44 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="11">
+  <si>
+    <t>mpg</t>
+  </si>
+  <si>
+    <t>cyl</t>
+  </si>
+  <si>
+    <t>disp</t>
+  </si>
+  <si>
+    <t>hp</t>
+  </si>
+  <si>
+    <t>drat</t>
+  </si>
+  <si>
+    <t>wt</t>
+  </si>
+  <si>
+    <t>qsec</t>
+  </si>
+  <si>
+    <t>vs</t>
+  </si>
+  <si>
+    <t>am</t>
+  </si>
+  <si>
+    <t>gear</t>
+  </si>
+  <si>
+    <t>carb</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -355,64 +393,42 @@
   <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>mpg</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>cyl</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>disp</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>hp</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>drat</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>wt</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>qsec</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>am</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>gear</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>carb</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:11" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>18.7</v>
       </c>
@@ -447,7 +463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>14.3</v>
       </c>
@@ -482,7 +498,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>16.4</v>
       </c>
@@ -517,7 +533,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>17.3</v>
       </c>
@@ -552,7 +568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>15.2</v>
       </c>
@@ -587,7 +603,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>10.4</v>
       </c>
@@ -622,7 +638,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>10.4</v>
       </c>
@@ -657,7 +673,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>14.7</v>
       </c>
@@ -692,7 +708,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>15.5</v>
       </c>
@@ -727,7 +743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>15.2</v>
       </c>
@@ -762,7 +778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>13.3</v>
       </c>
@@ -797,7 +813,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>19.2</v>
       </c>
@@ -842,64 +858,42 @@
   <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>mpg</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>cyl</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>disp</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>hp</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>drat</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>wt</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>qsec</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>am</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>gear</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>carb</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:11" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>15.8</v>
       </c>
@@ -934,7 +928,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>15</v>
       </c>
